--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2081.93</v>
+        <v>-2086.89</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,52 +1445,52 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2032.94</v>
+        <v>-2081.93</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,74 +1876,74 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2019.36</v>
+        <v>-2032.94</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,67 +2307,67 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1851.76</v>
+        <v>-2019.36</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1839.46</v>
+        <v>-1851.76</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
+          <t>-315.1879199591352</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1688.57</v>
+        <v>-1839.46</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-27.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-75.74</t>
+          <t>-76.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1608.0</t>
+          <t>19531.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3189.2</t>
+          <t>6388.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7490.0</t>
+          <t>8786.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8046.26</t>
+          <t>8377.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4300</t>
+          <t>-2398</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>262.0467421890224</t>
+          <t>-38.04831906451668</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-2868.68</v>
+        <v>-1688.57</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-57.42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,37 +4031,37 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4071,32 +4071,32 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.30</t>
+          <t>-75.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3285.0</t>
+          <t>1608.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4833.4</t>
+          <t>3189.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9237.3</t>
+          <t>7490.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8087.98</t>
+          <t>8046.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4403</t>
+          <t>-4300</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>831.2697761848858</t>
+          <t>262.0467421890224</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2531.78</v>
+        <v>-2868.68</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>21.3</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>21.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-55.41</t>
+          <t>-47.68</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.48</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-74.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4217.0</t>
+          <t>3285.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8141.4</t>
+          <t>4833.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18257.1</t>
+          <t>9237.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8077.1</t>
+          <t>8087.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-10115</t>
+          <t>-4403</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1442.732528104552</t>
+          <t>831.2697761848858</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2139.74</v>
+        <v>-2531.78</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,22 +4705,22 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,72 +4772,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-55.41</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-67.69</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>21.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-12.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3302.0</t>
+          <t>4217.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8988.8</t>
+          <t>8141.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27823.9</t>
+          <t>18257.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8049.46</t>
+          <t>8077.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-18835</t>
+          <t>-10115</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2094.091372737073</t>
+          <t>1442.732528104552</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1603.13</v>
+        <v>-2139.74</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-63.91</t>
+          <t>-67.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-6.30</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,67 +5324,67 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.02</t>
+          <t>-72.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60830.46164978293</t>
+          <t>60749.14378612716</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3534.0</t>
+          <t>3302.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>11184.8</t>
+          <t>8988.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>30987.2</t>
+          <t>27823.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8102.62</t>
+          <t>8049.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-19802</t>
+          <t>-18835</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2766.313443683733</t>
+          <t>2094.091372737073</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-681.25</v>
+        <v>-1603.13</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>12.93680419660917</t>
+          <t>9.539363848845143</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3.103925054318688</t>
+          <t>7.303962001194574</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-13.54295778129747</t>
+          <t>-9.184780184239289</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,260 +1024,260 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>60669.82467532467</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-1977.07</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>69.05</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>60749.14378612716</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-2086.89</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>68.62</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,102 +1334,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-23.69</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>27.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-3.48</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-16.52</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.88</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-13.71</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>27.55</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-16.52</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2081.93</v>
+        <v>-2086.89</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1871,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2032.94</v>
+        <v>-2081.93</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,79 +2302,79 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-2019.36</v>
+        <v>-2032.94</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1851.76</v>
+        <v>-2019.36</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-8.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1839.46</v>
+        <v>-1851.76</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
+          <t>-315.1879199591352</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1688.57</v>
+        <v>-1839.46</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-27.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-75.74</t>
+          <t>-76.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1608.0</t>
+          <t>19531.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3189.2</t>
+          <t>6388.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7490.0</t>
+          <t>8786.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8046.26</t>
+          <t>8377.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4300</t>
+          <t>-2398</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>262.0467421890224</t>
+          <t>-38.04831906451668</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2868.68</v>
+        <v>-1688.57</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-57.42</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,212 +4457,212 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>21.32</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>20.26</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-23.72</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-75.74</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>60669.82467532467</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>1608.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>3189.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>7490.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>8046.26</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-4300</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>262.0467421890224</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2868.68</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-10.13</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>4.37</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>21.32</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.23</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20.29</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-20.00</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-74.30</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>60749.14378612716</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>3285.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4833.4</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>9237.3</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8087.98</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-4403</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>831.2697761848858</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-2531.78</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-10.76</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
           <t>2.51</t>
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>21.3</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>21.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-55.41</t>
+          <t>-47.68</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.48</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-74.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4217.0</t>
+          <t>3285.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8141.4</t>
+          <t>4833.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18257.1</t>
+          <t>9237.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8077.1</t>
+          <t>8087.98</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-10115</t>
+          <t>-4403</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1442.732528104552</t>
+          <t>831.2697761848858</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2139.74</v>
+        <v>-2531.78</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,72 +5203,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.68</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-55.41</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-3.61</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-67.69</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>21.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-12.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-73.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60749.14378612716</t>
+          <t>60669.82467532467</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3302.0</t>
+          <t>4217.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8988.8</t>
+          <t>8141.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27823.9</t>
+          <t>18257.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8049.46</t>
+          <t>8077.1</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-18835</t>
+          <t>-10115</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2094.091372737073</t>
+          <t>1442.732528104552</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1603.13</v>
+        <v>-2139.74</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1977.07</v>
+        <v>-1987.72</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,260 +1455,260 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>60586.78746397694</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1977.07</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>70.03</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>60669.82467532467</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-2086.89</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>69.05</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1871,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2081.93</v>
+        <v>-2086.89</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,57 +2302,57 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-2032.94</v>
+        <v>-2081.93</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>-8.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,79 +2733,79 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-2019.36</v>
+        <v>-2032.94</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.82</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,72 +3164,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1851.76</v>
+        <v>-2019.36</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-9.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1839.46</v>
+        <v>-1851.76</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
+          <t>-315.1879199591352</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1688.57</v>
+        <v>-1839.46</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-27.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-75.74</t>
+          <t>-76.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1608.0</t>
+          <t>19531.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3189.2</t>
+          <t>6388.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7490.0</t>
+          <t>8786.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8046.26</t>
+          <t>8377.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4300</t>
+          <t>-2398</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>262.0467421890224</t>
+          <t>-38.04831906451668</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2868.68</v>
+        <v>-1688.57</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-57.42</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,42 +4888,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4933,32 +4933,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.30</t>
+          <t>-75.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3285.0</t>
+          <t>1608.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4833.4</t>
+          <t>3189.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9237.3</t>
+          <t>7490.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8087.98</t>
+          <t>8046.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4403</t>
+          <t>-4300</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>831.2697761848858</t>
+          <t>262.0467421890224</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2531.78</v>
+        <v>-2868.68</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>21.3</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>21.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-55.41</t>
+          <t>-47.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.48</t>
+          <t>-20.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.02</t>
+          <t>-74.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60669.82467532467</t>
+          <t>60586.78746397694</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4217.0</t>
+          <t>3285.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8141.4</t>
+          <t>4833.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18257.1</t>
+          <t>9237.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8077.1</t>
+          <t>8087.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-10115</t>
+          <t>-4403</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1442.732528104552</t>
+          <t>831.2697761848858</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2139.74</v>
+        <v>-2531.78</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>70.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3361.8</t>
+          <t>2816.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8590.32</t>
+          <t>8585.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1987.72</v>
+        <v>-1961.31</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1977.07</v>
+        <v>-1987.72</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,260 +1886,260 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>60503.53381294964</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-1977.07</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>72.55</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>1627</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>60586.78746397694</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-2086.89</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>4.94</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>70.03</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,52 +2307,52 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-2081.93</v>
+        <v>-2086.89</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.64</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,52 +2738,52 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-2032.94</v>
+        <v>-2081.93</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,74 +3169,74 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-2019.36</v>
+        <v>-2032.94</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.63</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,67 +3600,67 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1851.76</v>
+        <v>-2019.36</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-7.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1839.46</v>
+        <v>-1851.76</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
+          <t>-315.1879199591352</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1688.57</v>
+        <v>-1839.46</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-27.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-75.74</t>
+          <t>-76.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1608.0</t>
+          <t>19531.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3189.2</t>
+          <t>6388.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7490.0</t>
+          <t>8786.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8046.26</t>
+          <t>8377.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4300</t>
+          <t>-2398</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>262.0467421890224</t>
+          <t>-38.04831906451668</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2868.68</v>
+        <v>-1688.57</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-57.42</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,37 +5324,37 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,32 +5364,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.00</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.30</t>
+          <t>-75.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60586.78746397694</t>
+          <t>60503.53381294964</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3285.0</t>
+          <t>1608.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4833.4</t>
+          <t>3189.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9237.3</t>
+          <t>7490.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8087.98</t>
+          <t>8046.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4403</t>
+          <t>-4300</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>831.2697761848858</t>
+          <t>262.0467421890224</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2531.78</v>
+        <v>-2868.68</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>21.3</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>21.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2816.0</t>
+          <t>2684.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8585.34</t>
+          <t>8595.48</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-1961.31</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1599.594666207477</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1828.610087609776</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>2686</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-13.08</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-14.77</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3361.8</t>
+          <t>2816.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8590.32</t>
+          <t>8585.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1987.72</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1557.955498679786</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1961.307673549836</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>1817</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-14.56</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-13.08</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1891,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1977.07</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1484.618739612504</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1987.721807980284</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2028</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-13.92</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-14.56</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,273 +2337,278 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>60422.39224137932</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>3854</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>72.85</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>60503.53381294964</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2086.89</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>1627</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,52 +2763,52 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,175 +2848,175 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-2081.93</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1286.976743623861</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-2086.894395372471</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>3039</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-9.70</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-12.24</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,20 +3026,25 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,52 +3199,52 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-2032.94</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1141.537170578659</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-2081.928211749148</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>3342</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-7.17</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-9.70</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,74 +3635,74 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-2019.36</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-970.5569812749333</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-2032.943370439071</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>4546</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-5.91</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-7.17</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.77</t>
+          <t>-10.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4071,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1851.76</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-777.3958196087264</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-2019.359905337568</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>3836</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-6.33</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-5.91</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-9.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-1839.46</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-551.5841676580278</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1851.763530001937</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>6573</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-8.02</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-6.33</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-1688.57</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-315.1879199591352</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1839.455724879537</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>5942</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-5.06</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-8.02</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>870.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-27.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-75.74</t>
+          <t>-76.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60503.53381294964</t>
+          <t>60422.39224137932</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1608.0</t>
+          <t>19531.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3189.2</t>
+          <t>6388.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7490.0</t>
+          <t>8786.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8046.26</t>
+          <t>8377.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4300</t>
+          <t>-2398</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>262.0467421890224</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2868.68</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-38.04831906451668</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1688.571155958982</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>19531</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-10.13</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-5.06</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電子零組件業右下上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,210 +1019,210 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>21.34</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>60340.33428981349</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2507.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>8556.14</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>2152</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>60422.39224137932</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2684.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>8595.48</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>2686</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2816.0</t>
+          <t>2684.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8585.34</t>
+          <t>8595.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1817</v>
+        <v>2686</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3361.8</t>
+          <t>2816.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8590.32</t>
+          <t>8585.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2028</v>
+        <v>1817</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3854</v>
+        <v>2028</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>-2.97</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,265 +2773,265 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>60340.33428981349</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>3854</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>74.18</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>60422.39224137932</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-2086.894395372471</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>3039</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>72.85</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,52 +3199,52 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2081.928211749148</t>
+          <t>-2086.894395372471</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>3342</v>
+        <v>3039</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,52 +3635,52 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2032.943370439071</t>
+          <t>-2081.928211749148</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>4546</v>
+        <v>3342</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.4</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,74 +4071,74 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2019.359905337568</t>
+          <t>-2032.943370439071</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>3836</v>
+        <v>4546</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.9</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,67 +4507,67 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1851.763530001937</t>
+          <t>-2019.359905337568</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>6573</v>
+        <v>3836</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1839.455724879537</t>
+          <t>-1851.763530001937</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>5942</v>
+        <v>6573</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>870.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.29</t>
+          <t>-13.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.34</t>
+          <t>-76.97</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60422.39224137932</t>
+          <t>60340.33428981349</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19531.0</t>
+          <t>5942.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6388.6</t>
+          <t>6916.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8786.7</t>
+          <t>7952.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8377.36</t>
+          <t>8437.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2398</t>
+          <t>-1036</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-38.04831906451668</t>
+          <t>-315.1879199591352</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1688.571155958982</t>
+          <t>-1839.455724879537</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>19531</v>
+        <v>5942</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,52 +1019,52 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2507.4</t>
+          <t>2699.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8556.14</t>
+          <t>8612.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2152</v>
+        <v>4816</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,210 +1455,210 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>21.34</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>60264.23638968481</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2507.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>8556.14</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2152</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>60340.33428981349</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2684.8</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>8595.48</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>2686</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2816.0</t>
+          <t>2684.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8585.34</t>
+          <t>8595.48</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1817</v>
+        <v>2686</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3361.8</t>
+          <t>2816.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8590.32</t>
+          <t>8585.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2028</v>
+        <v>1817</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3854</v>
+        <v>2028</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,265 +3209,265 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>60264.23638968481</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>3854</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>72.32</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>60340.33428981349</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-2086.894395372471</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>3039</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>74.18</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>1623</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,52 +3635,52 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2081.928211749148</t>
+          <t>-2086.894395372471</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>3342</v>
+        <v>3039</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,52 +4071,52 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2032.943370439071</t>
+          <t>-2081.928211749148</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4546</v>
+        <v>3342</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,74 +4507,74 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2019.359905337568</t>
+          <t>-2032.943370439071</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>3836</v>
+        <v>4546</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,67 +4943,67 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1851.763530001937</t>
+          <t>-2019.359905337568</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>6573</v>
+        <v>3836</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.03</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.62</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.97</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60340.33428981349</t>
+          <t>60264.23638968481</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5942.0</t>
+          <t>6573.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6916.6</t>
+          <t>7387.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7952.7</t>
+          <t>7764.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8437.2</t>
+          <t>8516.04</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1036</t>
+          <t>-376</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-315.1879199591352</t>
+          <t>-551.5841676580278</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1839.455724879537</t>
+          <t>-1851.763530001937</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>5942</v>
+        <v>6573</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2699.8</t>
+          <t>3087.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8612.56</t>
+          <t>8617.94</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4816</v>
+        <v>3968</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,57 +1450,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2507.4</t>
+          <t>2699.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8556.14</t>
+          <t>8612.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2152</v>
+        <v>4816</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,215 +1886,215 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>21.34</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>60186.53648068669</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2507.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>8556.14</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2152</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>60264.23638968481</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2684.8</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8595.48</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>2686</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2816.0</t>
+          <t>2684.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8585.34</t>
+          <t>8595.48</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1817</v>
+        <v>2686</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3361.8</t>
+          <t>2816.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8590.32</t>
+          <t>8585.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>2028</v>
+        <v>1817</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3723.4</t>
+          <t>3361.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8609.2</t>
+          <t>8590.32</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>3854</v>
+        <v>2028</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,265 +3645,265 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>60186.53648068669</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>3723.4</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>8609.2</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>3854</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>72.24</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>60264.23638968481</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-2086.894395372471</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>3039</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,57 +4066,57 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4847.8</t>
+          <t>4267.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>8539.9</t>
+          <t>8563.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2081.928211749148</t>
+          <t>-2086.894395372471</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>3342</v>
+        <v>3039</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,57 +4502,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8085.6</t>
+          <t>4847.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>8514.7</t>
+          <t>8539.9</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2032.943370439071</t>
+          <t>-2081.928211749148</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>4546</v>
+        <v>3342</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,79 +4938,79 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7498.0</t>
+          <t>8085.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>8528.94</t>
+          <t>8514.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2019.359905337568</t>
+          <t>-2032.943370439071</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>3836</v>
+        <v>4546</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,72 +5374,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.33</t>
+          <t>-77.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60264.23638968481</t>
+          <t>60186.53648068669</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6573.0</t>
+          <t>3836.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7387.8</t>
+          <t>7498.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7764.6</t>
+          <t>6165.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>8516.04</t>
+          <t>8528.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-376</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-551.5841676580278</t>
+          <t>-777.3958196087264</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1851.763530001937</t>
+          <t>-2019.359905337568</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>6573</v>
+        <v>3836</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>20.79</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3968.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3087.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3087.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>3224.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>8617.94</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>8617.940000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1227.739943281262</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3968</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3968.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4816.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2699.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2699.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3211.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>8612.56</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>8612.559999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1418.017618486152</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4816</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4816.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>20.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2152.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2507.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2507.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3387.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8556.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>8556.139999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1730.05652526149</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2152</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>20.45</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2684.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2684.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>3766.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>8595.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>8595.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1828.610087609776</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>20.69</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.57</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.57</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1817.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2816.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2816</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5450.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8585.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8585.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1961.307673549836</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1817</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1817.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>20.97</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21.67</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.56</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.56</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2028.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3361.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>3361.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5429.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8590.32</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8590.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1987.721807980284</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2028</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2028.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>3854.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3723.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>3723.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5555.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8609.2</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8609.200000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1977.073364024486</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>3854</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>21.74</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.97</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.53</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.53</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3039.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>4267.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>4267.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5591.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8563.76</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8563.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2086.894395372471</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3039</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3039.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>21.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.51</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.51</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3342.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4847.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>4847.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>5618.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8539.9</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8539.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2081.928211749148</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3342</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3342.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>22.16</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.48</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>4546.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>8085.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>8085.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5637.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8514.7</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8514.700000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2032.943370439071</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>4546</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>4546.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>22.02</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.44</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.44</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3836.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>7498.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>7498</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>6165.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8528.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8528.940000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2019.359905337568</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3836</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3836.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,69 +898,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.54</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-02-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-02-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,209 +2304,209 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>60104.265</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>60186.53648068669</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2816</v>
+        <v>2684.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8585.34</v>
+        <v>8595.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.67</v>
+        <v>21.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3361.8</v>
+        <v>2816</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8590.32</v>
+        <v>8585.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.81</v>
+        <v>21.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.55</v>
+        <v>20.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3723.4</v>
+        <v>3361.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8609.200000000001</v>
+        <v>8590.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,259 +4039,259 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.97</v>
+        <v>21.81</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.53</v>
+        <v>20.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>60104.265</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>3723.4</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8609.200000000001</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>72.42</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>20.4</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>60186.53648068669</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>4267.2</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>8563.76</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-2086.894395372471</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>72.24</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>20.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.71</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.01</v>
+        <v>21.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.51</v>
+        <v>20.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-34.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-80.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4847.8</v>
+        <v>4267.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5618.2</t>
+          <t>5591.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8539.9</v>
+        <v>8563.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-770</t>
+          <t>-1324</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1141.537170578659</t>
+          <t>-1286.976743623861</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2081.928211749148</t>
+          <t>-2086.894395372471</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3342.0</t>
+          <t>3039.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.70</t>
+          <t>-12.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>-13.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.92</v>
+        <v>22.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.48</v>
+        <v>20.51</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.77</t>
+          <t>-78.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8085.6</v>
+        <v>4847.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5637.4</t>
+          <t>5618.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8514.700000000001</v>
+        <v>8539.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-970.5569812749333</t>
+          <t>-1141.537170578659</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2032.943370439071</t>
+          <t>-2081.928211749148</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4546.0</t>
+          <t>3342.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,75 +5314,75 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.78</v>
+        <v>21.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.44</v>
+        <v>20.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-77.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>60186.53648068669</t>
+          <t>60104.265</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7498</v>
+        <v>8085.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6165.7</t>
+          <t>5637.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8528.940000000001</v>
+        <v>8514.700000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-777.3958196087264</t>
+          <t>-970.5569812749333</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2019.359905337568</t>
+          <t>-2032.943370439071</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3836.0</t>
+          <t>4546.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>3390</t>
@@ -879,77 +883,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-22 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -984,313 +988,4613 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>92.59</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>89.28</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-97.97</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2674.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>2977.6</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2742.5</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>8668.299999999999</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-1388.335476646623</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1084.714670100229</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2674.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>92.59</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.38</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-32.19</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-98.43</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1699.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>2873.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2779.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8632.1</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-1443.539259655059</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1205.957385396593</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1699.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-8.86</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>77.78</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.92</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.37</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-159.81</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-98.30</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1731.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>3070.6</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2943.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>8624.200000000001</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-1486.735964065689</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1231.627072055807</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1731.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-10.34</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>184.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>54.63</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-182.15</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-97.62</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>3968.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>3087.8</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>3224.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8617.940000000001</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-1533.119398976577</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1227.739943281262</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3968.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-9.07</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-15.94</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>47.22</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>20.53</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-232.44</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-96.53</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>4816.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>2699.8</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>3211.6</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8612.559999999999</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-511</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-1588.642936375725</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-1418.017618486152</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4816.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-11.18</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-25.98</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>16.67</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-4.42</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-28.72</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-4.56</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-148.89</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-91.79</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2686.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>2684.8</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>3766.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>8595.48</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-1081</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1599.594666207477</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-1828.610087609776</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2686.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-14.77</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-48.34</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>17.07</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>20.69</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>20.36</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-103.74</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-88.74</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1817.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5450.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8585.34</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-2634</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1557.955498679786</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1961.307673549836</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1817.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-13.08</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-38.09</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-3.43</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>20.97</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.37</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-84.37</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-85.81</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2028.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>3361.8</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>5429.9</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8590.32</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-2068</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-1484.618739612504</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1987.721807980284</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2028.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-14.56</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-32.98</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-4.58</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>21.38</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>3723.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8609.200000000001</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-23.69</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>27.16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-4.32</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>21.74</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-34.58</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-80.34</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>59942.3717948718</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>3039.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>4267.2</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>5591.9</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>8563.76</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-1324</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1286.976743623861</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-2086.894395372471</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3039.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-12.24</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>73.73</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>73.82</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,33 +993,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1049,38 +1049,38 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,14 +1296,14 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,84 +2188,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,209 +3594,209 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>59873.57325746799</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>59942.3717948718</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2816</v>
+        <v>2684.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8585.34</v>
+        <v>8595.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.67</v>
+        <v>21.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3361.8</v>
+        <v>2816</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8590.32</v>
+        <v>8585.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.81</v>
+        <v>21.67</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.55</v>
+        <v>20.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59942.3717948718</t>
+          <t>59873.57325746799</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3723.4</v>
+        <v>3361.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8609.200000000001</v>
+        <v>8590.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-32.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,261 +5329,261 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.97</v>
+        <v>21.81</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.53</v>
+        <v>20.55</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-57.74</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-82.82</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>59873.57325746799</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>3723.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>5555.6</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>8609.200000000001</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-1832</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1393.145454454726</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1977.073364024486</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3854.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>13.56%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>73.78</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>旭軟-電子零組件業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>21.15</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-34.58</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-80.34</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>59942.3717948718</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>4267.2</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>5591.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>8563.76</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1324</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-1286.976743623861</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-2086.894395372471</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>3039.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-12.24</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>13.56%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>73.82</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>旭軟-電子零組件業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>18.0</t>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,33 +1423,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,17 +1459,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1479,38 +1479,38 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,84 +2618,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,209 +4024,209 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>59803.74928977272</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>59873.57325746799</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2816</v>
+        <v>2684.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8585.34</v>
+        <v>8595.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.67</v>
+        <v>21.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3361.8</v>
+        <v>2816</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8590.32</v>
+        <v>8585.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.98</t>
+          <t>-38.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.81</v>
+        <v>21.67</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.55</v>
+        <v>20.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-57.74</t>
+          <t>-84.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59873.57325746799</t>
+          <t>59803.74928977272</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3723.4</v>
+        <v>3361.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5555.6</t>
+          <t>5429.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8609.200000000001</v>
+        <v>8590.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1832</t>
+          <t>-2068</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1393.145454454726</t>
+          <t>-1484.618739612504</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1977.073364024486</t>
+          <t>-1987.721807980284</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>2028.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>76.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,33 +993,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,33 +1853,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,17 +1889,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1909,38 +1909,38 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,84 +3048,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,209 +4454,209 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>59737.7744680851</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>59803.74928977272</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-103.74</t>
+          <t>-148.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2816</v>
+        <v>2684.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8585.34</v>
+        <v>8595.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.09</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.67</v>
+        <v>21.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.56</v>
+        <v>20.57</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-84.37</t>
+          <t>-103.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-88.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59803.74928977272</t>
+          <t>59737.7744680851</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3361.8</v>
+        <v>2816</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5429.9</t>
+          <t>5450.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8590.32</v>
+        <v>8585.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2068</t>
+          <t>-2634</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1484.618739612504</t>
+          <t>-1557.955498679786</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1987.721807980284</t>
+          <t>-1961.307673549836</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2028.0</t>
+          <t>1817.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.56</t>
+          <t>-13.08</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1032,56 +1032,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
+      <c r="AH2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.99</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>21.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>107.61</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
+          <t>89.86</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.17</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,33 +1415,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1462,56 +1454,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.08</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>130.45</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
+          <t>107.61</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.13</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1892,56 +1876,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="AH4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.24</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>143.28</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+          <t>130.45</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2164,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -2268,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,33 +2259,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,18 +2295,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.59</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.74</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2339,39 +2311,35 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.28</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
+          <t>143.28</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,12 +2606,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2658,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2683,7 +2651,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2752,56 +2720,48 @@
           <t>92.59</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.19</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
+          <t>89.28</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.04</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
+          <t>92.59</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.38</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-159.81</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
+          <t>-32.19</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.03</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,84 +3430,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5.97</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.63</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.66</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-182.15</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>-159.81</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.04</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
+          <t>54.63</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-232.44</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+          <t>-182.15</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.05</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4390,50 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-4.42</t>
-        </is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-3.64</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,18 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-199.35</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
+          <t>-232.44</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,209 +4812,201 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.69</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-4.56</t>
-        </is>
+          <t>11.25</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-4.42</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>59662.25354107648</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>59737.7744680851</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-28.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5252,48 @@
           <t>5.69</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-4.56</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.57</v>
+        <v>20.58</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-103.74</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
+          <t>-148.89</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.17</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-88.74</t>
+          <t>-91.79</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59737.7744680851</t>
+          <t>59662.25354107648</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2816</v>
+        <v>2684.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5450.8</t>
+          <t>3766.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8585.34</v>
+        <v>8595.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2634</t>
+          <t>-1081</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1557.955498679786</t>
+          <t>-1599.594666207477</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1961.307673549836</t>
+          <t>-1828.610087609776</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1817.0</t>
+          <t>2686.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.08</t>
+          <t>-14.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>78.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>21.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,33 +1837,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,74 +2586,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,33 +2681,33 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,14 +2717,14 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -2733,35 +2733,35 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.66</v>
+        <v>-0.38</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,84 +3852,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.66</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.28</v>
+        <v>-1.66</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.53</v>
+        <v>3.66</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.64</v>
+        <v>-2.28</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,50 +4812,50 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.74</v>
+        <v>2.53</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.42</v>
+        <v>-3.64</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59662.25354107648</t>
+          <t>59587.64851485148</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-28.72</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,201 +5234,201 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.22</v>
+        <v>0.74</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.56</v>
+        <v>-4.42</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>20.34</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-199.35</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-94.52</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>59587.64851485148</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>2507.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>3387.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>8556.139999999999</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-879</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1619.665721446556</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1730.05652526149</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2152.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-13.29</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>20.45</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-148.89</t>
-        </is>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-91.79</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>59662.25354107648</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>2684.8</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>3766.3</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>8595.48</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1081</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-1599.594666207477</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-1828.610087609776</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>2686.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-14.77</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.66</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,75 +1014,75 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6523</v>
+        <v>5465.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4750.3</t>
+          <t>4511.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9130.76</v>
+        <v>9141.299999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>953</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-678.562801841614</t>
+          <t>-613.0243369956273</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-61.20480353905805</t>
+          <t>-252.5627803427005</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>21.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,33 +2259,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,74 +3008,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,33 +3103,33 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -3155,35 +3155,35 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.66</v>
+        <v>-0.38</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,84 +4274,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5.69</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.66</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.28</v>
+        <v>-1.66</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.53</v>
+        <v>3.66</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.64</v>
+        <v>-2.28</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,50 +5234,50 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.74</v>
+        <v>2.53</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.42</v>
+        <v>-3.64</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.53</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-199.35</t>
+          <t>-232.44</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-96.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59587.64851485148</t>
+          <t>59508.63559322034</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2507.4</v>
+        <v>2699.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3387.3</t>
+          <t>3211.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8556.139999999999</v>
+        <v>8612.559999999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-879</t>
+          <t>-511</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1619.665721446556</t>
+          <t>-1588.642936375725</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1730.05652526149</t>
+          <t>-1418.017618486152</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2152.0</t>
+          <t>4816.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AQ2" t="n">
         <v>0.41</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5465.6</v>
+        <v>4741.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4511.8</t>
+          <t>4467.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9141.299999999999</v>
+        <v>9184.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-613.0243369956273</t>
+          <t>-564.5704843188668</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-252.5627803427005</t>
+          <t>-298.0742945966831</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,75 +1436,75 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6523</v>
+        <v>5465.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4750.3</t>
+          <t>4511.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9130.76</v>
+        <v>9141.299999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>953</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-678.562801841614</t>
+          <t>-613.0243369956273</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-61.20480353905805</t>
+          <t>-252.5627803427005</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>21.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,33 +2681,33 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,74 +3430,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,33 +3525,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,14 +3561,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -3577,35 +3577,35 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3820,14 +3820,14 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3987,47 +3987,47 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.66</v>
+        <v>-0.38</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,84 +4696,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.66</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.28</v>
+        <v>-1.66</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>54.63</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>2.53</v>
+        <v>3.66</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.64</v>
+        <v>-2.28</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.64</v>
+        <v>20.68</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-232.44</t>
+          <t>-182.15</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-96.53</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59508.63559322034</t>
+          <t>59432.16220028209</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2699.8</v>
+        <v>3087.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3211.6</t>
+          <t>3224.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8612.559999999999</v>
+        <v>8617.940000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-511</t>
+          <t>-137</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1588.642936375725</t>
+          <t>-1533.119398976577</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1418.017618486152</t>
+          <t>-1227.739943281262</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4816.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.75</v>
+        <v>-0.93</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.57</v>
+        <v>21.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.22</v>
+        <v>21.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.32</t>
+          <t>-85.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4741.8</v>
+        <v>3382</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4467.6</t>
+          <t>4500.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9184.18</v>
+        <v>9195.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-1118</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-564.5704843188668</t>
+          <t>-544.2181786097417</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-298.0742945966831</t>
+          <t>-432.2804972095541</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AQ3" t="n">
         <v>0.41</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5465.6</v>
+        <v>4741.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4511.8</t>
+          <t>4467.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9141.299999999999</v>
+        <v>9184.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-613.0243369956273</t>
+          <t>-564.5704843188668</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-252.5627803427005</t>
+          <t>-298.0742945966831</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,75 +1858,75 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6523</v>
+        <v>5465.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4750.3</t>
+          <t>4511.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9130.76</v>
+        <v>9141.299999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>953</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-678.562801841614</t>
+          <t>-613.0243369956273</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-61.20480353905805</t>
+          <t>-252.5627803427005</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>21.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,33 +3103,33 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,74 +3852,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -3999,35 +3999,35 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.66</v>
+        <v>-0.38</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.72</v>
+        <v>20.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-159.81</t>
+          <t>-32.19</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-98.30</t>
+          <t>-98.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3070.6</v>
+        <v>2873.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2943.3</t>
+          <t>2779.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8624.200000000001</v>
+        <v>8632.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>94</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1486.735964065689</t>
+          <t>-1443.539259655059</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1231.627072055807</t>
+          <t>-1205.957385396593</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1731.0</t>
+          <t>1699.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>21.75</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,84 +5118,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.66</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.28</v>
+        <v>-1.66</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.28</v>
+        <v>21.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.68</v>
+        <v>20.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-182.15</t>
+          <t>-159.81</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-98.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>59432.16220028209</t>
+          <t>59352.81126760563</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3087.8</v>
+        <v>3070.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>2943.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8617.940000000001</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1533.119398976577</t>
+          <t>-1486.735964065689</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1227.739943281262</t>
+          <t>-1231.627072055807</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>1731.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -923,167 +923,167 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-49.47</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>-0.22</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-35.81</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1109,51 +1109,51 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>40.21</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-0.93</v>
+        <v>-0.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.26</v>
+        <v>3.36</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>21.64</v>
+        <v>21.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>21.33</v>
+        <v>21.39</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-84.27</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,48 +1172,48 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>1871.0</t>
+          <t>1136.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>2900.2</v>
+        <v>2205.2</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>4517.9</t>
+          <t>4364.1</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>9195.780000000001</v>
+        <v>9195.6</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-1617</t>
+          <t>-2158</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-541.9912013787546</t>
+          <t>-557.0460760162165</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-529.7428266083252</t>
+          <t>-639.8478865222569</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1871.0</t>
+          <t>1136.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
           <t>22.25</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>22.35</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-35.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1561,61 +1561,61 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>40.21</t>
         </is>
       </c>
       <c r="AP3" t="n">
         <v>-0.93</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.72</v>
+        <v>4.26</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>21.59</v>
+        <v>21.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>21.28</v>
+        <v>21.33</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-85.25</t>
+          <t>-84.56</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>3382</v>
+        <v>2900.2</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>4500.7</t>
+          <t>4517.9</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>9195.52</v>
+        <v>9195.780000000001</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-1118</t>
+          <t>-1617</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-544.2181786097417</t>
+          <t>-541.9912013787546</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-432.2804972095541</t>
+          <t>-529.7428266083252</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>22.35</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>22.4</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2023,61 +2023,61 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-0.75</v>
+        <v>-0.93</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>21.57</v>
+        <v>21.59</v>
       </c>
       <c r="AV4" t="n">
-        <v>21.22</v>
+        <v>21.28</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-86.32</t>
+          <t>-85.25</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,48 +2096,48 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>4741.8</v>
+        <v>3382</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>4467.6</t>
+          <t>4500.7</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>9184.18</v>
+        <v>9195.52</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-1118</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-564.5704843188668</t>
+          <t>-544.2181786097417</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-298.0742945966831</t>
+          <t>-432.2804972095541</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2485,61 +2485,61 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AV5" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>0.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.32</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,48 +2558,48 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>5465.6</v>
+        <v>4741.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>4511.8</t>
+          <t>4467.6</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>9141.299999999999</v>
+        <v>9184.18</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-613.0243369956273</t>
+          <t>-564.5704843188668</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-252.5627803427005</t>
+          <t>-298.0742945966831</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2947,70 +2947,70 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,48 +3020,48 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>6523</v>
+        <v>5465.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>4750.3</t>
+          <t>4511.8</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>9130.76</v>
+        <v>9141.299999999999</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>953</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-678.562801841614</t>
+          <t>-613.0243369956273</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-61.20480353905805</t>
+          <t>-252.5627803427005</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3423,47 +3423,47 @@
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AV7" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,48 +3482,48 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3885,47 +3885,47 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AU8" t="n">
         <v>21.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,48 +3944,48 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4302,27 +4302,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4347,47 +4347,47 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AV9" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,48 +4406,48 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>345.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4809,47 +4809,47 @@
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AV10" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,48 +4868,48 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,94 +5096,94 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -5226,27 +5226,27 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
@@ -5283,35 +5283,35 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AV11" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,48 +5330,48 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5578,74 +5578,74 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -5693,17 +5693,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5733,47 +5733,47 @@
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.38</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>21.28</v>
+        <v>21.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>20.77</v>
+        <v>20.82</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-32.19</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-98.43</t>
+          <t>-97.97</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,135 +5792,135 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>59273.2805907173</t>
+          <t>59192.42485955056</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>2873.2</v>
+        <v>2977.6</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2779.0</t>
+          <t>2742.5</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>8632.1</v>
+        <v>8668.299999999999</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>235</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-1443.539259655059</t>
+          <t>-1388.335476646623</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-1205.957385396593</t>
+          <t>-1084.714670100229</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1699.0</t>
+          <t>2674.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-7.59</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-8.86</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>4.47</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>78.62</t>
+          <t>78.28</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>17.54</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>3.36</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>22.44</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>21.71</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>21.39</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>20.74</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>7.50</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.35</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.33</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-84.27</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1136.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>2205.2</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>4364.1</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>9195.6</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-2158</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-557.0460760162165</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-639.8478865222569</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>1136.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-6.12</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>22.1</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>22.45</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>22.1</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>40.21</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.93</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>4.26</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>22.56</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>21.64</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>21.33</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>20.71</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>17.76</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.38</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.32</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-84.56</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>1871.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>2900.2</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>4517.9</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>9195.780000000001</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-1617</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-541.9912013787546</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-529.7428266083252</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>1871.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-5.70</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>22.35</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>2.14</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>52.63</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>71.46</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.93</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>4.72</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>2.91</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>22.61</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>21.59</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>21.28</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>20.68</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>29.08</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.4</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.31</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-85.25</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>2062.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>3382</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>4500.7</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>9195.52</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-1118</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-544.2181786097417</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-432.2804972095541</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>2062.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-5.49</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>22.35</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>22.5</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>22.25</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>3.62</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.11</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>87.25</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>4.87</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>2.82</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>22.62</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>21.57</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>21.22</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>20.64</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>43.43</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.41</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.29</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-86.32</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>3526.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>4741.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>4467.6</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>9184.18</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-564.5704843188668</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-298.0742945966831</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>3526.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-5.27</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>22.35</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>22.45</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>93.75</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>97.92</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.62</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>4.86</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>2.73</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>22.61</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>21.56</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>21.16</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>62.63</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.41</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-87.81</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>2431.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>5465.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>4511.8</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>9141.299999999999</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>953</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-613.0243369956273</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-252.5627803427005</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>2431.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-4.01</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>4.72</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>1.42</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>4.62</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>2.66</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>22.53</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>21.54</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>21.1</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>78.40</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.38</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.21</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-89.71</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>4611.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>6523</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>4750.3</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>9130.76</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1772</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-678.562801841614</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-61.20480353905805</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>4611.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-3.59</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>4.46</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>1.16</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>3.99</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>2.13</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>22.34</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>21.48</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>21.03</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>20.51</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>89.86</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.33</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.17</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-91.73</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>4280.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>6135.6</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>4504.4</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>9083.700000000001</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1631</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-790.8097106238969</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-19.22180797888632</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>4280.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-4.64</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>22.6</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>22.6</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>22.1</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>22.6</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>9.01</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-5.12</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>3.08</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>2.39</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>22.14</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>21.48</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>20.98</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>20.47</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>107.61</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.28</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.13</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-93.59</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>8861.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>5619.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>4345.0</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>9028.34</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-931.098420195717</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>76.9046788206042</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>8861.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-5.27</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>23.6</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>22.45</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>22.45</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>7.39</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>2.28</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>2.24</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>21.42</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>20.92</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>20.44</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>130.45</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.23</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-95.31</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>7145.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>4193.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>3640.6</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>8887.9</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>552</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-1114.371710925957</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-279.3397928522882</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>7145.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-5.49</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>22.6</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>22.1</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>22.4</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>8.01</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>2.85</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>1.74</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>21.73</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>21.36</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>20.88</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>20.42</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>143.28</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.16</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-96.84</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>7718.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>3558</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>3128.9</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>8799.139999999999</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>429</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-1266.195696030261</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-594.426902640268</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>7718.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-5.70</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>22.35</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/08/15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/03/28</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>25.25</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>2.86</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>92.59</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>2</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>21.47</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>21.3</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>20.82</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>89.28</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.08</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.04</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-97.97</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>59192.42485955056</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>2674.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>2977.6</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>2742.5</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>8668.299999999999</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-1388.335476646623</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-1084.714670100229</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>2674.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-7.59</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>旭軟</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>9.539363848845143</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>7.303962001194574</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-9.184780184239289</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>4.49</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>13.56%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-5.17%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>78.28</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>軟性印刷電路板(FPC)98.07%、其他1.93% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>旭軟-電子零組件業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>21.5</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 觸控面板 - 軟性電路板** 印刷電路板 - 硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-49.47</t>
+          <t>-42.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1093,37 +1093,37 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.85</v>
+        <v>-1.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.36</v>
+        <v>2.26</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>21.71</v>
+        <v>21.79</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21.39</v>
+        <v>21.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-84.27</t>
+          <t>-84.50</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1136.0</t>
+          <t>2465.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>2205.2</v>
+        <v>2212</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>4364.1</t>
+          <t>3838.8</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>9195.6</v>
+        <v>9203.459999999999</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2158</t>
+          <t>-1626</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-557.0460760162165</t>
+          <t>-563.8467152904835</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-639.8478865222569</t>
+          <t>-601.2502312989527</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1136.0</t>
+          <t>2465.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,187 +1425,187 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-49.47</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>-0.22</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-35.81</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,51 +1631,51 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>40.21</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.93</v>
+        <v>-0.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.26</v>
+        <v>3.36</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>21.64</v>
+        <v>21.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21.33</v>
+        <v>21.39</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>-84.27</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1871.0</t>
+          <t>1136.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>2900.2</v>
+        <v>2205.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>4517.9</t>
+          <t>4364.1</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>9195.780000000001</v>
+        <v>9195.6</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1617</t>
+          <t>-2158</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-541.9912013787546</t>
+          <t>-557.0460760162165</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-529.7428266083252</t>
+          <t>-639.8478865222569</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1871.0</t>
+          <t>1136.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>22.25</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>22.35</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-35.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2057,37 +2057,37 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>40.21</t>
         </is>
       </c>
       <c r="AT4" t="n">
         <v>-0.93</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.72</v>
+        <v>4.26</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>21.59</v>
+        <v>21.64</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21.28</v>
+        <v>21.33</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-85.25</t>
+          <t>-84.56</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>3382</v>
+        <v>2900.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>4500.7</t>
+          <t>4517.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>9195.52</v>
+        <v>9195.780000000001</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-1118</t>
+          <t>-1617</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-544.2181786097417</t>
+          <t>-541.9912013787546</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-432.2804972095541</t>
+          <t>-529.7428266083252</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>22.35</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>22.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2539,37 +2539,37 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.75</v>
+        <v>-0.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>21.57</v>
+        <v>21.59</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21.22</v>
+        <v>21.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-86.32</t>
+          <t>-85.25</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>4741.8</v>
+        <v>3382</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>4467.6</t>
+          <t>4500.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>9184.18</v>
+        <v>9195.52</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-1118</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-564.5704843188668</t>
+          <t>-544.2181786097417</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-298.0742945966831</t>
+          <t>-432.2804972095541</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>3526.0</t>
+          <t>2062.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3021,37 +3021,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="BC6" t="n">
         <v>0.41</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.32</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>5465.6</v>
+        <v>4741.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>4511.8</t>
+          <t>4467.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>9141.299999999999</v>
+        <v>9184.18</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-613.0243369956273</t>
+          <t>-564.5704843188668</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-252.5627803427005</t>
+          <t>-298.0742945966831</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3503,37 +3503,37 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,75 +3544,75 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-89.71</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>6523</v>
+        <v>5465.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>4750.3</t>
+          <t>4511.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>9130.76</v>
+        <v>9141.299999999999</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>953</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-678.562801841614</t>
+          <t>-613.0243369956273</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-61.20480353905805</t>
+          <t>-252.5627803427005</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4611.0</t>
+          <t>2431.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3985,37 +3985,37 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.99</v>
+        <v>4.62</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>21.48</v>
+        <v>21.54</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21.03</v>
+        <v>21.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>78.40</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-89.71</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>6135.6</v>
+        <v>6523</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>4504.4</t>
+          <t>4750.3</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>9083.700000000001</v>
+        <v>9130.76</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-790.8097106238969</t>
+          <t>-678.562801841614</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-19.22180797888632</t>
+          <t>-61.20480353905805</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4280.0</t>
+          <t>4611.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4467,37 +4467,37 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AY9" t="n">
         <v>21.48</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4949,53 +4949,53 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>21.42</v>
+        <v>21.48</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.92</v>
+        <v>20.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>20.47</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>130.45</t>
+          <t>107.61</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-95.31</t>
+          <t>-93.59</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>4193.4</v>
+        <v>5619.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>3640.6</t>
+          <t>4345.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>8887.9</v>
+        <v>9028.34</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1114.371710925957</t>
+          <t>-931.098420195717</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-279.3397928522882</t>
+          <t>76.9046788206042</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>7145.0</t>
+          <t>8861.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,187 +5281,187 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>318.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15.18</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>345.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.71</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.88</v>
+        <v>20.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.44</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>143.28</t>
+          <t>130.45</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-96.84</t>
+          <t>-95.31</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>3558</v>
+        <v>4193.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>3128.9</t>
+          <t>3640.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>8799.139999999999</v>
+        <v>8887.9</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>552</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1266.195696030261</t>
+          <t>-1114.371710925957</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-594.426902640268</t>
+          <t>-279.3397928522882</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>7718.0</t>
+          <t>7145.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,74 +5778,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13.71</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8.57</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5913,53 +5913,53 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>2025/11/03</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,14 +5969,14 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -5985,35 +5985,35 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>21.3</v>
+        <v>21.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.82</v>
+        <v>20.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>143.28</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-97.97</t>
+          <t>-96.84</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>59192.42485955056</t>
+          <t>59114.59186535764</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>2977.6</v>
+        <v>3558</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>2742.5</t>
+          <t>3128.9</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>8668.299999999999</v>
+        <v>8799.139999999999</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>429</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1388.335476646623</t>
+          <t>-1266.195696030261</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1084.714670100229</t>
+          <t>-594.426902640268</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2674.0</t>
+          <t>7718.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>77.49</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,172 +958,172 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-44.34</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-42.38</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,128 +1134,128 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>22.09</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-25.44</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-85.42</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>1609.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1828.6</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>3285.2</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>9213.860000000001</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-1456</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-573.0088539935115</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-623.4006168601654</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>1609.0</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>20.77</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-5.94</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-84.50</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>2465.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>2212</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>3838.8</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>9203.459999999999</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-1626</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-563.8467152904835</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-601.2502312989527</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>2465.0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-49.47</t>
+          <t>-42.38</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,213 +1616,213 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>20.77</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-5.94</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-84.50</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2465.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>2212</v>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>3838.8</t>
+        </is>
+      </c>
+      <c r="BL3" t="n">
+        <v>9203.459999999999</v>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-1626</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-563.8467152904835</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-601.2502312989527</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2465.0</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-7.38</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>20.74</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-84.27</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>1136.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>2205.2</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>4364.1</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>9195.6</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-2158</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-557.0460760162165</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-639.8478865222569</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>1136.0</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-6.12</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI3" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,187 +1907,187 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.49</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-49.47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>-0.22</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-35.81</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,213 +2098,213 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>17.54</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>22.44</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>20.74</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-84.27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>1136.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2205.2</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>4364.1</t>
+        </is>
+      </c>
+      <c r="BL4" t="n">
+        <v>9195.6</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-2158</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-557.0460760162165</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-639.8478865222569</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>1136.0</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>40.21</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>20.71</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-84.56</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>1871.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2900.2</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>4517.9</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>9195.780000000001</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-1617</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-541.9912013787546</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-529.7428266083252</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>1871.0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-5.70</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI4" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>22.25</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>22.35</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-35.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>40.21</t>
         </is>
       </c>
       <c r="AT5" t="n">
         <v>-0.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.72</v>
+        <v>4.26</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>21.59</v>
+        <v>21.64</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21.28</v>
+        <v>21.33</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-85.25</t>
+          <t>-84.56</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>59114.59186535764</t>
+          <t>59035.17857142858</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>3382</v>
+        <v>2900.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>4500.7</t>
+          <t>4517.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>9195.52</v>
+        <v>9195.780000000001</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-1118</t>
+          <t>-1617</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-544.2181786097417</t>
+          <t>-541.9912013787546</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-432.2804972095541</t>
+          <t>-529.7428266083252</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2062.0</t>
+          <t>1871.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>22.35</t>
-        </is>
-      </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>22.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,213 +3062,213 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>52.63</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>71.46</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>20.68</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-85.25</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>2062.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3382</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>4500.7</t>
+        </is>
+      </c>
+      <c r="BL6" t="n">
+        <v>9195.52</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-1118</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-544.2181786097417</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-432.2804972095541</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>2062.0</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-5.49</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>87.25</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>22.62</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>43.43</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-86.32</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>3526.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>4741.8</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>4467.6</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>9184.18</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-564.5704843188668</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-298.0742945966831</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>3526.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-5.27</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI6" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="BC7" t="n">
         <v>0.41</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.32</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>59114.59186535764</t>
+          <t>59035.17857142858</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>5465.6</v>
+        <v>4741.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>4511.8</t>
+          <t>4467.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>9141.299999999999</v>
+        <v>9184.18</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-613.0243369956273</t>
+          <t>-564.5704843188668</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-252.5627803427005</t>
+          <t>-298.0742945966831</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2431.0</t>
+          <t>3526.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,213 +4026,213 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>93.75</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>97.92</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>22.61</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>62.63</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>-87.81</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>2431.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>5465.6</v>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>4511.8</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
+        <v>9141.299999999999</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-613.0243369956273</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-252.5627803427005</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>2431.0</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-4.01</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>78.40</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-89.71</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>4611.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>6523</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>4750.3</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>9130.76</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1772</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-678.562801841614</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-61.20480353905805</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>4611.0</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI8" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,213 +4508,213 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>22.53</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>78.40</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-89.71</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>4611.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>6523</v>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>4750.3</t>
+        </is>
+      </c>
+      <c r="BL9" t="n">
+        <v>9130.76</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1772</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-678.562801841614</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-61.20480353905805</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>4611.0</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>20.51</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>89.86</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-91.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>4280.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>6135.6</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>4504.4</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
-        <v>9083.700000000001</v>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-790.8097106238969</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-19.22180797888632</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>4280.0</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-4.64</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI9" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>388.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.08</v>
+        <v>3.99</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AY10" t="n">
         <v>21.48</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.98</v>
+        <v>21.03</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.47</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>107.61</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-91.73</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>59114.59186535764</t>
+          <t>59035.17857142858</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>5619.4</v>
+        <v>6135.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>4345.0</t>
+          <t>4504.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>9028.34</v>
+        <v>9083.700000000001</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-931.098420195717</t>
+          <t>-790.8097106238969</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>76.9046788206042</t>
+          <t>-19.22180797888632</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>8861.0</t>
+          <t>4280.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>318.0</t>
+          <t>388.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,14 +5376,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,234 +5451,234 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>22.14</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>20.47</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>107.61</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-93.59</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>8861.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>5619.4</v>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>4345.0</t>
+        </is>
+      </c>
+      <c r="BL11" t="n">
+        <v>9028.34</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-931.098420195717</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>76.9046788206042</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>8861.0</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>-5.27</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>20.44</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>130.45</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-95.31</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>7145.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>4193.4</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>3640.6</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
-        <v>8887.9</v>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-1114.371710925957</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-279.3397928522882</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>7145.0</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-5.49</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI11" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,187 +5763,187 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>318.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15.18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>21.95</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>345.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>13.71</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,213 +5954,213 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>20.44</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>130.45</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>-95.31</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>59035.17857142858</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>7145.0</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4193.4</v>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>3640.6</t>
+        </is>
+      </c>
+      <c r="BL12" t="n">
+        <v>8887.9</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-1114.371710925957</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-279.3397928522882</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>7145.0</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>-5.49</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>旭軟</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>9.539363848845143</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>7.303962001194574</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>-9.184780184239289</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>21.73</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>143.28</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-96.84</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>59114.59186535764</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>7718.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>3558</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>3128.9</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
-        <v>8799.139999999999</v>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-1266.195696030261</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-594.426902640268</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>7718.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>-5.70</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>旭軟</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>9.539363848845143</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>7.303962001194574</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>-9.184780184239289</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI12" t="inlineStr">
         <is>
           <t>13.56%</t>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/軟性電路板.xlsx
+++ b/Result/checksun_type/軟性電路板.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.34</t>
+          <t>-35.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.67</v>
+        <v>-1.69</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>21.85</v>
+        <v>21.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21.48</v>
+        <v>21.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-39.50</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-85.42</t>
+          <t>-86.73</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>59035.17857142858</t>
+          <t>58954.78951048951</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1609.0</t>
+          <t>1038.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>1828.6</v>
+        <v>1623.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>3285.2</t>
+          <t>2502.9</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>9213.860000000001</v>
+        <v>9182.799999999999</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-1456</t>
+          <t>-879</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-573.0088539935115</t>
+          <t>-587.3376258916652</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-623.4006168601654</t>
+          <t>-666.1458713315105</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1609.0</t>
+          <t>1038.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>78.12</t>
+          <t>77.09</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-44.34</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-42.38</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>21.55</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/03/28</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>21.95</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>21.55</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/03/28</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/03</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>21.55</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1635,48 +1635,48 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.48</v>
+        <v>-2.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.26</v>
+        <v>1.1</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>21.79</v>
+        <v>21.85</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21.44</v>
+        <v>21.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="BC3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BD3" t="n">
         <v>0.3</v>
       </c>
-      <c r="BD3" t="n">
-        <v>0.32</v>
-      </c>
       <c r="BE3" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-84.50</t>
+          <t>-85.42</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>59035.17857142858</t>
+          <t>58954.78951048951</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2465.0</t>
+          <t>1609.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>2212</v>
+        <v>1828.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>3838.8</t>
+          <t>3285.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>9203.459999999999</v>
+        <v>9213.860000000001</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1626</t>
+          <t>-1456</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-563.8467152904835</t>
+          <t>-573.0088539935115</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-601.2502312989527</t>
+          <t>-623.4006168601654</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2465.0</t>
+          <t>1609.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b